--- a/TeplosilaWeb/Content/properties/gtrv3.xlsx
+++ b/TeplosilaWeb/Content/properties/gtrv3.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user29\Documents\ТЗ программа подбора TRV, RDT\ТЗ клапаны TRV\25.05.2026 (действ)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/22451d98f477d1d3/Рабочий стол/TeploSilaWeb/TeplosilaWeb/Content/properties/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FA783A7-D469-4CFC-B51D-F4CE1D9ED435}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{903E3C33-FD37-4579-9CE6-DBE773BA75F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -20,6 +20,9 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -85,9 +88,6 @@
     <t>TSL-3000-60-2A-230-IP67</t>
   </si>
   <si>
-    <t>TW5000-XD220-S.14</t>
-  </si>
-  <si>
     <t>TSL-1600-25-2AR-230-IP67</t>
   </si>
   <si>
@@ -152,13 +152,16 @@
   </si>
   <si>
     <t>TSL-3000-60-2М-230-IP67</t>
+  </si>
+  <si>
+    <t>TSL-10000-60-3A-230-IP65</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -211,6 +214,14 @@
       <family val="2"/>
       <charset val="204"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -256,7 +267,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -283,6 +294,12 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -583,23 +600,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
-      <c r="J1" s="13"/>
-      <c r="K1" s="13"/>
-      <c r="L1" s="13"/>
-      <c r="M1" s="13"/>
-      <c r="N1" s="13"/>
-      <c r="O1" s="13"/>
+      <c r="A1" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
+      <c r="N1" s="15"/>
+      <c r="O1" s="15"/>
     </row>
     <row r="2" spans="1:15" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
@@ -608,21 +625,21 @@
       <c r="B2" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="12"/>
-      <c r="J2" s="12"/>
-      <c r="K2" s="12"/>
-      <c r="L2" s="12"/>
-      <c r="M2" s="12"/>
-      <c r="N2" s="12"/>
-      <c r="O2" s="12"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
+      <c r="J2" s="14"/>
+      <c r="K2" s="14"/>
+      <c r="L2" s="14"/>
+      <c r="M2" s="14"/>
+      <c r="N2" s="14"/>
+      <c r="O2" s="14"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="8">
@@ -668,7 +685,7 @@
         <v>200</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
@@ -769,29 +786,29 @@
       <c r="A6" s="8">
         <v>4</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="11"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="11"/>
-      <c r="H6" s="11"/>
-      <c r="I6" s="11"/>
-      <c r="J6" s="11"/>
-      <c r="K6" s="11"/>
-      <c r="L6" s="11"/>
-      <c r="M6" s="11"/>
-      <c r="N6" s="11"/>
-      <c r="O6" s="11"/>
+      <c r="C6" s="13"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="13"/>
+      <c r="J6" s="13"/>
+      <c r="K6" s="13"/>
+      <c r="L6" s="13"/>
+      <c r="M6" s="13"/>
+      <c r="N6" s="13"/>
+      <c r="O6" s="13"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="8">
         <v>5</v>
       </c>
-      <c r="B7" s="10" t="s">
-        <v>39</v>
+      <c r="B7" s="4" t="s">
+        <v>38</v>
       </c>
       <c r="C7" s="3">
         <v>315</v>
@@ -824,7 +841,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C8" s="3">
         <v>315</v>
@@ -890,7 +907,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C10" s="3">
         <v>315</v>
@@ -923,7 +940,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C11" s="3">
         <v>315</v>
@@ -1022,7 +1039,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C14" s="3">
         <v>315</v>
@@ -1055,7 +1072,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C15" s="3">
         <v>315</v>
@@ -1121,7 +1138,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C17" s="3">
         <v>315</v>
@@ -1154,7 +1171,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C18" s="3">
         <v>315</v>
@@ -1186,8 +1203,8 @@
       <c r="A19" s="8">
         <v>17</v>
       </c>
-      <c r="B19" s="10" t="s">
-        <v>40</v>
+      <c r="B19" s="4" t="s">
+        <v>39</v>
       </c>
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
@@ -1214,7 +1231,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
@@ -1268,7 +1285,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
@@ -1299,7 +1316,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
@@ -1326,7 +1343,7 @@
         <v>22</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C24" s="3"/>
       <c r="D24" s="3"/>
@@ -1407,7 +1424,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
@@ -1434,7 +1451,7 @@
         <v>26</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
@@ -1488,7 +1505,7 @@
         <v>28</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C30" s="3"/>
       <c r="D30" s="3"/>
@@ -1515,7 +1532,7 @@
         <v>29</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
@@ -1541,8 +1558,8 @@
       <c r="A32" s="8">
         <v>30</v>
       </c>
-      <c r="B32" s="10" t="s">
-        <v>41</v>
+      <c r="B32" s="4" t="s">
+        <v>40</v>
       </c>
       <c r="C32" s="3"/>
       <c r="D32" s="3"/>
@@ -1567,7 +1584,7 @@
         <v>31</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
@@ -1592,7 +1609,7 @@
         <v>32</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C34" s="3"/>
       <c r="D34" s="3"/>
@@ -1692,57 +1709,57 @@
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A38" s="8">
+      <c r="A38" s="11">
         <v>36</v>
       </c>
-      <c r="B38" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C38" s="3"/>
-      <c r="D38" s="3"/>
-      <c r="E38" s="3"/>
-      <c r="F38" s="3"/>
-      <c r="G38" s="3"/>
-      <c r="H38" s="3"/>
-      <c r="I38" s="3"/>
-      <c r="J38" s="3"/>
-      <c r="K38" s="3"/>
-      <c r="L38" s="3"/>
-      <c r="M38" s="3"/>
-      <c r="N38" s="3">
-        <v>500</v>
-      </c>
-      <c r="O38" s="3">
-        <v>570</v>
+      <c r="B38" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="C38" s="12"/>
+      <c r="D38" s="12"/>
+      <c r="E38" s="12"/>
+      <c r="F38" s="12"/>
+      <c r="G38" s="12"/>
+      <c r="H38" s="12"/>
+      <c r="I38" s="12"/>
+      <c r="J38" s="12"/>
+      <c r="K38" s="12"/>
+      <c r="L38" s="12"/>
+      <c r="M38" s="12"/>
+      <c r="N38" s="12">
+        <v>740</v>
+      </c>
+      <c r="O38" s="12">
+        <v>810</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="8">
         <v>37</v>
       </c>
-      <c r="B39" s="11" t="s">
+      <c r="B39" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="C39" s="11"/>
-      <c r="D39" s="11"/>
-      <c r="E39" s="11"/>
-      <c r="F39" s="11"/>
-      <c r="G39" s="11"/>
-      <c r="H39" s="11"/>
-      <c r="I39" s="11"/>
-      <c r="J39" s="11"/>
-      <c r="K39" s="11"/>
-      <c r="L39" s="11"/>
-      <c r="M39" s="11"/>
-      <c r="N39" s="11"/>
-      <c r="O39" s="11"/>
+      <c r="C39" s="13"/>
+      <c r="D39" s="13"/>
+      <c r="E39" s="13"/>
+      <c r="F39" s="13"/>
+      <c r="G39" s="13"/>
+      <c r="H39" s="13"/>
+      <c r="I39" s="13"/>
+      <c r="J39" s="13"/>
+      <c r="K39" s="13"/>
+      <c r="L39" s="13"/>
+      <c r="M39" s="13"/>
+      <c r="N39" s="13"/>
+      <c r="O39" s="13"/>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="8">
         <v>38</v>
       </c>
-      <c r="B40" s="10" t="s">
-        <v>39</v>
+      <c r="B40" s="4" t="s">
+        <v>38</v>
       </c>
       <c r="C40" s="3">
         <v>6.3</v>
@@ -1775,7 +1792,7 @@
         <v>39</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C41" s="3">
         <v>6.3</v>
@@ -1841,7 +1858,7 @@
         <v>41</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C43" s="3">
         <v>6.3</v>
@@ -1874,7 +1891,7 @@
         <v>42</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C44" s="3">
         <v>6.3</v>
@@ -1973,7 +1990,7 @@
         <v>45</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C47" s="3">
         <v>6.3</v>
@@ -2006,7 +2023,7 @@
         <v>46</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C48" s="3">
         <v>6.3</v>
@@ -2072,7 +2089,7 @@
         <v>48</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C50" s="3">
         <v>6.3</v>
@@ -2105,7 +2122,7 @@
         <v>49</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C51" s="3">
         <v>6.3</v>
@@ -2137,8 +2154,8 @@
       <c r="A52" s="8">
         <v>50</v>
       </c>
-      <c r="B52" s="10" t="s">
-        <v>40</v>
+      <c r="B52" s="4" t="s">
+        <v>39</v>
       </c>
       <c r="C52" s="3"/>
       <c r="D52" s="3"/>
@@ -2165,7 +2182,7 @@
         <v>51</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
@@ -2219,7 +2236,7 @@
         <v>53</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C55" s="3"/>
       <c r="D55" s="3"/>
@@ -2250,7 +2267,7 @@
         <v>54</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C56" s="3"/>
       <c r="D56" s="3"/>
@@ -2277,7 +2294,7 @@
         <v>55</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C57" s="3"/>
       <c r="D57" s="3"/>
@@ -2358,7 +2375,7 @@
         <v>58</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C60" s="3"/>
       <c r="D60" s="3"/>
@@ -2385,7 +2402,7 @@
         <v>59</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C61" s="3"/>
       <c r="D61" s="3"/>
@@ -2439,7 +2456,7 @@
         <v>61</v>
       </c>
       <c r="B63" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C63" s="3"/>
       <c r="D63" s="3"/>
@@ -2466,7 +2483,7 @@
         <v>62</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C64" s="3"/>
       <c r="D64" s="3"/>
@@ -2492,8 +2509,8 @@
       <c r="A65" s="8">
         <v>63</v>
       </c>
-      <c r="B65" s="10" t="s">
-        <v>41</v>
+      <c r="B65" s="4" t="s">
+        <v>40</v>
       </c>
       <c r="C65" s="3"/>
       <c r="D65" s="3"/>
@@ -2518,7 +2535,7 @@
         <v>64</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C66" s="3"/>
       <c r="D66" s="3"/>
@@ -2543,7 +2560,7 @@
         <v>65</v>
       </c>
       <c r="B67" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C67" s="3"/>
       <c r="D67" s="3"/>
@@ -2643,28 +2660,28 @@
       </c>
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A71" s="8">
+      <c r="A71" s="11">
         <v>69</v>
       </c>
-      <c r="B71" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C71" s="3"/>
-      <c r="D71" s="3"/>
-      <c r="E71" s="3"/>
-      <c r="F71" s="3"/>
-      <c r="G71" s="3"/>
-      <c r="H71" s="3"/>
-      <c r="I71" s="3"/>
-      <c r="J71" s="3"/>
-      <c r="K71" s="3"/>
-      <c r="L71" s="3"/>
-      <c r="M71" s="3"/>
-      <c r="N71" s="3">
-        <v>68</v>
-      </c>
-      <c r="O71" s="3">
-        <v>78</v>
+      <c r="B71" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="C71" s="12"/>
+      <c r="D71" s="12"/>
+      <c r="E71" s="12"/>
+      <c r="F71" s="12"/>
+      <c r="G71" s="12"/>
+      <c r="H71" s="12"/>
+      <c r="I71" s="12"/>
+      <c r="J71" s="12"/>
+      <c r="K71" s="12"/>
+      <c r="L71" s="12"/>
+      <c r="M71" s="12"/>
+      <c r="N71" s="12">
+        <v>81.5</v>
+      </c>
+      <c r="O71" s="12">
+        <v>91.5</v>
       </c>
     </row>
   </sheetData>

--- a/TeplosilaWeb/Content/properties/gtrv3.xlsx
+++ b/TeplosilaWeb/Content/properties/gtrv3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/22451d98f477d1d3/Рабочий стол/TeploSilaWeb/TeplosilaWeb/Content/properties/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{903E3C33-FD37-4579-9CE6-DBE773BA75F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{37A9E05C-218E-40D1-8FCF-0C0BD1D83341}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="43">
   <si>
     <t>Наименование параметров,
 единицы измерения</t>
@@ -155,6 +155,9 @@
   </si>
   <si>
     <t>TSL-10000-60-3A-230-IP65</t>
+  </si>
+  <si>
+    <t>TSL-5000-60-2A-230-IP67</t>
   </si>
 </sst>
 </file>
@@ -590,7 +593,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O71"/>
+  <dimension ref="A1:O73"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="6" customWidth="1"/>
@@ -1680,119 +1683,115 @@
       <c r="O36" s="3"/>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A37" s="8">
+      <c r="A37" s="11">
         <v>35</v>
       </c>
-      <c r="B37" s="4" t="s">
+      <c r="B37" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C37" s="12"/>
+      <c r="D37" s="12"/>
+      <c r="E37" s="12"/>
+      <c r="F37" s="12"/>
+      <c r="G37" s="12"/>
+      <c r="H37" s="12"/>
+      <c r="I37" s="12"/>
+      <c r="J37" s="12"/>
+      <c r="K37" s="12"/>
+      <c r="L37" s="12">
+        <v>510</v>
+      </c>
+      <c r="M37" s="12">
+        <v>540</v>
+      </c>
+      <c r="N37" s="12">
+        <v>545</v>
+      </c>
+      <c r="O37" s="12">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A38" s="8">
+        <v>36</v>
+      </c>
+      <c r="B38" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C37" s="3"/>
-      <c r="D37" s="3"/>
-      <c r="E37" s="3"/>
-      <c r="F37" s="3"/>
-      <c r="G37" s="3"/>
-      <c r="H37" s="3"/>
-      <c r="I37" s="3"/>
-      <c r="J37" s="3"/>
-      <c r="K37" s="3"/>
-      <c r="L37" s="3">
+      <c r="C38" s="3"/>
+      <c r="D38" s="3"/>
+      <c r="E38" s="3"/>
+      <c r="F38" s="3"/>
+      <c r="G38" s="3"/>
+      <c r="H38" s="3"/>
+      <c r="I38" s="3"/>
+      <c r="J38" s="3"/>
+      <c r="K38" s="3"/>
+      <c r="L38" s="3">
         <v>540</v>
       </c>
-      <c r="M37" s="3">
+      <c r="M38" s="3">
         <v>570</v>
       </c>
-      <c r="N37" s="3">
+      <c r="N38" s="3">
         <v>575</v>
       </c>
-      <c r="O37" s="3">
+      <c r="O38" s="3">
         <v>645</v>
-      </c>
-    </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A38" s="11">
-        <v>36</v>
-      </c>
-      <c r="B38" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="C38" s="12"/>
-      <c r="D38" s="12"/>
-      <c r="E38" s="12"/>
-      <c r="F38" s="12"/>
-      <c r="G38" s="12"/>
-      <c r="H38" s="12"/>
-      <c r="I38" s="12"/>
-      <c r="J38" s="12"/>
-      <c r="K38" s="12"/>
-      <c r="L38" s="12"/>
-      <c r="M38" s="12"/>
-      <c r="N38" s="12">
-        <v>740</v>
-      </c>
-      <c r="O38" s="12">
-        <v>810</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="8">
         <v>37</v>
       </c>
-      <c r="B39" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="C39" s="13"/>
-      <c r="D39" s="13"/>
-      <c r="E39" s="13"/>
-      <c r="F39" s="13"/>
-      <c r="G39" s="13"/>
-      <c r="H39" s="13"/>
-      <c r="I39" s="13"/>
-      <c r="J39" s="13"/>
-      <c r="K39" s="13"/>
-      <c r="L39" s="13"/>
-      <c r="M39" s="13"/>
-      <c r="N39" s="13"/>
-      <c r="O39" s="13"/>
+      <c r="B39" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C39" s="3"/>
+      <c r="D39" s="3"/>
+      <c r="E39" s="3"/>
+      <c r="F39" s="3"/>
+      <c r="G39" s="3"/>
+      <c r="H39" s="3"/>
+      <c r="I39" s="3"/>
+      <c r="J39" s="3"/>
+      <c r="K39" s="3"/>
+      <c r="L39" s="3"/>
+      <c r="M39" s="3"/>
+      <c r="N39" s="3">
+        <v>740</v>
+      </c>
+      <c r="O39" s="3">
+        <v>810</v>
+      </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="8">
         <v>38</v>
       </c>
-      <c r="B40" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C40" s="3">
-        <v>6.3</v>
-      </c>
-      <c r="D40" s="3">
-        <v>7.2</v>
-      </c>
-      <c r="E40" s="3">
-        <v>8.1999999999999993</v>
-      </c>
-      <c r="F40" s="3">
-        <v>10.8</v>
-      </c>
-      <c r="G40" s="3">
-        <v>12.3</v>
-      </c>
-      <c r="H40" s="3">
-        <v>14.8</v>
-      </c>
-      <c r="I40" s="3"/>
-      <c r="J40" s="3"/>
-      <c r="K40" s="3"/>
-      <c r="L40" s="3"/>
-      <c r="M40" s="3"/>
-      <c r="N40" s="3"/>
-      <c r="O40" s="3"/>
+      <c r="B40" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="C40" s="13"/>
+      <c r="D40" s="13"/>
+      <c r="E40" s="13"/>
+      <c r="F40" s="13"/>
+      <c r="G40" s="13"/>
+      <c r="H40" s="13"/>
+      <c r="I40" s="13"/>
+      <c r="J40" s="13"/>
+      <c r="K40" s="13"/>
+      <c r="L40" s="13"/>
+      <c r="M40" s="13"/>
+      <c r="N40" s="13"/>
+      <c r="O40" s="13"/>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="8">
         <v>39</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="C41" s="3">
         <v>6.3</v>
@@ -1825,7 +1824,7 @@
         <v>40</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="C42" s="3">
         <v>6.3</v>
@@ -1858,7 +1857,7 @@
         <v>41</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="C43" s="3">
         <v>6.3</v>
@@ -1890,8 +1889,8 @@
       <c r="A44" s="8">
         <v>42</v>
       </c>
-      <c r="B44" s="9" t="s">
-        <v>29</v>
+      <c r="B44" s="4" t="s">
+        <v>35</v>
       </c>
       <c r="C44" s="3">
         <v>6.3</v>
@@ -1923,8 +1922,8 @@
       <c r="A45" s="8">
         <v>43</v>
       </c>
-      <c r="B45" s="4" t="s">
-        <v>10</v>
+      <c r="B45" s="9" t="s">
+        <v>29</v>
       </c>
       <c r="C45" s="3">
         <v>6.3</v>
@@ -1957,7 +1956,7 @@
         <v>44</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C46" s="3">
         <v>6.3</v>
@@ -1990,7 +1989,7 @@
         <v>45</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="C47" s="3">
         <v>6.3</v>
@@ -2023,7 +2022,7 @@
         <v>46</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C48" s="3">
         <v>6.3</v>
@@ -2056,7 +2055,7 @@
         <v>47</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C49" s="3">
         <v>6.3</v>
@@ -2088,8 +2087,8 @@
       <c r="A50" s="8">
         <v>48</v>
       </c>
-      <c r="B50" s="9" t="s">
-        <v>30</v>
+      <c r="B50" s="4" t="s">
+        <v>13</v>
       </c>
       <c r="C50" s="3">
         <v>6.3</v>
@@ -2121,8 +2120,8 @@
       <c r="A51" s="8">
         <v>49</v>
       </c>
-      <c r="B51" s="4" t="s">
-        <v>20</v>
+      <c r="B51" s="9" t="s">
+        <v>30</v>
       </c>
       <c r="C51" s="3">
         <v>6.3</v>
@@ -2155,23 +2154,29 @@
         <v>50</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="C52" s="3"/>
-      <c r="D52" s="3"/>
-      <c r="E52" s="3"/>
-      <c r="F52" s="3"/>
-      <c r="G52" s="3"/>
-      <c r="H52" s="3"/>
-      <c r="I52" s="3">
-        <v>19</v>
-      </c>
-      <c r="J52" s="3">
-        <v>23.4</v>
-      </c>
-      <c r="K52" s="3">
-        <v>29.6</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="C52" s="3">
+        <v>6.3</v>
+      </c>
+      <c r="D52" s="3">
+        <v>7.2</v>
+      </c>
+      <c r="E52" s="3">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="F52" s="3">
+        <v>10.8</v>
+      </c>
+      <c r="G52" s="3">
+        <v>12.3</v>
+      </c>
+      <c r="H52" s="3">
+        <v>14.8</v>
+      </c>
+      <c r="I52" s="3"/>
+      <c r="J52" s="3"/>
+      <c r="K52" s="3"/>
       <c r="L52" s="3"/>
       <c r="M52" s="3"/>
       <c r="N52" s="3"/>
@@ -2182,7 +2187,7 @@
         <v>51</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
@@ -2209,7 +2214,7 @@
         <v>52</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="C54" s="3"/>
       <c r="D54" s="3"/>
@@ -2235,8 +2240,8 @@
       <c r="A55" s="8">
         <v>53</v>
       </c>
-      <c r="B55" s="9" t="s">
-        <v>31</v>
+      <c r="B55" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="C55" s="3"/>
       <c r="D55" s="3"/>
@@ -2253,12 +2258,8 @@
       <c r="K55" s="3">
         <v>29.6</v>
       </c>
-      <c r="L55" s="3">
-        <v>36</v>
-      </c>
-      <c r="M55" s="3">
-        <v>55.8</v>
-      </c>
+      <c r="L55" s="3"/>
+      <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
     </row>
@@ -2266,8 +2267,8 @@
       <c r="A56" s="8">
         <v>54</v>
       </c>
-      <c r="B56" s="4" t="s">
-        <v>36</v>
+      <c r="B56" s="9" t="s">
+        <v>31</v>
       </c>
       <c r="C56" s="3"/>
       <c r="D56" s="3"/>
@@ -2284,8 +2285,12 @@
       <c r="K56" s="3">
         <v>29.6</v>
       </c>
-      <c r="L56" s="3"/>
-      <c r="M56" s="3"/>
+      <c r="L56" s="3">
+        <v>36</v>
+      </c>
+      <c r="M56" s="3">
+        <v>55.8</v>
+      </c>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
     </row>
@@ -2293,8 +2298,8 @@
       <c r="A57" s="8">
         <v>55</v>
       </c>
-      <c r="B57" s="9" t="s">
-        <v>32</v>
+      <c r="B57" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="C57" s="3"/>
       <c r="D57" s="3"/>
@@ -2320,8 +2325,8 @@
       <c r="A58" s="8">
         <v>56</v>
       </c>
-      <c r="B58" s="4" t="s">
-        <v>11</v>
+      <c r="B58" s="9" t="s">
+        <v>32</v>
       </c>
       <c r="C58" s="3"/>
       <c r="D58" s="3"/>
@@ -2348,7 +2353,7 @@
         <v>57</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C59" s="3"/>
       <c r="D59" s="3"/>
@@ -2375,7 +2380,7 @@
         <v>58</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C60" s="3"/>
       <c r="D60" s="3"/>
@@ -2402,7 +2407,7 @@
         <v>59</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C61" s="3"/>
       <c r="D61" s="3"/>
@@ -2429,7 +2434,7 @@
         <v>60</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C62" s="3"/>
       <c r="D62" s="3"/>
@@ -2455,8 +2460,8 @@
       <c r="A63" s="8">
         <v>61</v>
       </c>
-      <c r="B63" s="9" t="s">
-        <v>33</v>
+      <c r="B63" s="4" t="s">
+        <v>15</v>
       </c>
       <c r="C63" s="3"/>
       <c r="D63" s="3"/>
@@ -2482,8 +2487,8 @@
       <c r="A64" s="8">
         <v>62</v>
       </c>
-      <c r="B64" s="4" t="s">
-        <v>22</v>
+      <c r="B64" s="9" t="s">
+        <v>33</v>
       </c>
       <c r="C64" s="3"/>
       <c r="D64" s="3"/>
@@ -2510,7 +2515,7 @@
         <v>63</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="C65" s="3"/>
       <c r="D65" s="3"/>
@@ -2518,15 +2523,17 @@
       <c r="F65" s="3"/>
       <c r="G65" s="3"/>
       <c r="H65" s="3"/>
-      <c r="I65" s="3"/>
-      <c r="J65" s="3"/>
-      <c r="K65" s="3"/>
-      <c r="L65" s="3">
-        <v>36</v>
-      </c>
-      <c r="M65" s="3">
-        <v>55.8</v>
-      </c>
+      <c r="I65" s="3">
+        <v>19</v>
+      </c>
+      <c r="J65" s="3">
+        <v>23.4</v>
+      </c>
+      <c r="K65" s="3">
+        <v>29.6</v>
+      </c>
+      <c r="L65" s="3"/>
+      <c r="M65" s="3"/>
       <c r="N65" s="3"/>
       <c r="O65" s="3"/>
     </row>
@@ -2535,7 +2542,7 @@
         <v>64</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C66" s="3"/>
       <c r="D66" s="3"/>
@@ -2559,8 +2566,8 @@
       <c r="A67" s="8">
         <v>65</v>
       </c>
-      <c r="B67" s="9" t="s">
-        <v>34</v>
+      <c r="B67" s="4" t="s">
+        <v>37</v>
       </c>
       <c r="C67" s="3"/>
       <c r="D67" s="3"/>
@@ -2584,8 +2591,8 @@
       <c r="A68" s="8">
         <v>66</v>
       </c>
-      <c r="B68" s="4" t="s">
-        <v>18</v>
+      <c r="B68" s="9" t="s">
+        <v>34</v>
       </c>
       <c r="C68" s="3"/>
       <c r="D68" s="3"/>
@@ -2610,7 +2617,7 @@
         <v>67</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C69" s="3"/>
       <c r="D69" s="3"/>
@@ -2635,7 +2642,7 @@
         <v>68</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C70" s="3"/>
       <c r="D70" s="3"/>
@@ -2647,24 +2654,20 @@
       <c r="J70" s="3"/>
       <c r="K70" s="3"/>
       <c r="L70" s="3">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M70" s="3">
-        <v>56.8</v>
-      </c>
-      <c r="N70" s="3">
-        <v>68</v>
-      </c>
-      <c r="O70" s="3">
-        <v>78</v>
-      </c>
+        <v>55.8</v>
+      </c>
+      <c r="N70" s="3"/>
+      <c r="O70" s="3"/>
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" s="11">
         <v>69</v>
       </c>
       <c r="B71" s="10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C71" s="12"/>
       <c r="D71" s="12"/>
@@ -2675,12 +2678,70 @@
       <c r="I71" s="12"/>
       <c r="J71" s="12"/>
       <c r="K71" s="12"/>
-      <c r="L71" s="12"/>
-      <c r="M71" s="12"/>
+      <c r="L71" s="12">
+        <v>36.5</v>
+      </c>
+      <c r="M71" s="12">
+        <v>56.3</v>
+      </c>
       <c r="N71" s="12">
+        <v>67.5</v>
+      </c>
+      <c r="O71" s="12">
+        <v>77.5</v>
+      </c>
+    </row>
+    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A72" s="8">
+        <v>70</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C72" s="3"/>
+      <c r="D72" s="3"/>
+      <c r="E72" s="3"/>
+      <c r="F72" s="3"/>
+      <c r="G72" s="3"/>
+      <c r="H72" s="3"/>
+      <c r="I72" s="3"/>
+      <c r="J72" s="3"/>
+      <c r="K72" s="3"/>
+      <c r="L72" s="3">
+        <v>37</v>
+      </c>
+      <c r="M72" s="3">
+        <v>56.8</v>
+      </c>
+      <c r="N72" s="3">
+        <v>68</v>
+      </c>
+      <c r="O72" s="3">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A73" s="8">
+        <v>71</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C73" s="3"/>
+      <c r="D73" s="3"/>
+      <c r="E73" s="3"/>
+      <c r="F73" s="3"/>
+      <c r="G73" s="3"/>
+      <c r="H73" s="3"/>
+      <c r="I73" s="3"/>
+      <c r="J73" s="3"/>
+      <c r="K73" s="3"/>
+      <c r="L73" s="3"/>
+      <c r="M73" s="3"/>
+      <c r="N73" s="3">
         <v>81.5</v>
       </c>
-      <c r="O71" s="12">
+      <c r="O73" s="3">
         <v>91.5</v>
       </c>
     </row>
@@ -2688,7 +2749,7 @@
   <mergeCells count="4">
     <mergeCell ref="B6:O6"/>
     <mergeCell ref="C2:O2"/>
-    <mergeCell ref="B39:O39"/>
+    <mergeCell ref="B40:O40"/>
     <mergeCell ref="A1:O1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
